--- a/data/MelodyOfLife17Lineup.xlsx
+++ b/data/MelodyOfLife17Lineup.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\melody-of-life-17-planner\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\melody-of-life-planner\production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2519456-8926-4368-94AE-1A0FCA87B20A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E4E718-00C4-4C4F-80F5-1751F9550723}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -309,9 +309,6 @@
     <t>JAAR PROUDPETCH</t>
   </si>
   <si>
-    <t>HATABITO</t>
-  </si>
-  <si>
     <t>QViNT</t>
   </si>
   <si>
@@ -337,6 +334,9 @@
   </si>
   <si>
     <t>MANG</t>
+  </si>
+  <si>
+    <t>HATOBITO</t>
   </si>
 </sst>
 </file>
@@ -3232,7 +3232,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C72" s="22">
         <v>46312</v>
@@ -3261,7 +3261,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C73" s="22">
         <v>46312</v>
@@ -3290,7 +3290,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C74" s="22">
         <v>46312</v>
@@ -3406,7 +3406,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C78" s="22">
         <v>46313</v>
@@ -3435,7 +3435,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C79" s="22">
         <v>46313</v>
@@ -3464,7 +3464,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C80" s="22">
         <v>46313</v>
@@ -3493,7 +3493,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C81" s="22">
         <v>46313</v>
@@ -3522,7 +3522,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C82" s="22">
         <v>46313</v>
@@ -3551,7 +3551,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C83" s="22">
         <v>46313</v>
@@ -3638,7 +3638,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C86" s="22">
         <v>46313</v>
